--- a/artfynd/A 26488-2025 artfynd.xlsx
+++ b/artfynd/A 26488-2025 artfynd.xlsx
@@ -1738,7 +1738,7 @@
         <v>130157689</v>
       </c>
       <c r="B12" t="n">
-        <v>92959</v>
+        <v>92961</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 26488-2025 artfynd.xlsx
+++ b/artfynd/A 26488-2025 artfynd.xlsx
@@ -1738,7 +1738,7 @@
         <v>130157689</v>
       </c>
       <c r="B12" t="n">
-        <v>92961</v>
+        <v>93048</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 26488-2025 artfynd.xlsx
+++ b/artfynd/A 26488-2025 artfynd.xlsx
@@ -1738,7 +1738,7 @@
         <v>130157689</v>
       </c>
       <c r="B12" t="n">
-        <v>93048</v>
+        <v>93051</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 26488-2025 artfynd.xlsx
+++ b/artfynd/A 26488-2025 artfynd.xlsx
@@ -1738,7 +1738,7 @@
         <v>130157689</v>
       </c>
       <c r="B12" t="n">
-        <v>93051</v>
+        <v>93077</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 26488-2025 artfynd.xlsx
+++ b/artfynd/A 26488-2025 artfynd.xlsx
@@ -1738,7 +1738,7 @@
         <v>130157689</v>
       </c>
       <c r="B12" t="n">
-        <v>93077</v>
+        <v>93078</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 26488-2025 artfynd.xlsx
+++ b/artfynd/A 26488-2025 artfynd.xlsx
@@ -1738,7 +1738,7 @@
         <v>130157689</v>
       </c>
       <c r="B12" t="n">
-        <v>93078</v>
+        <v>93079</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 26488-2025 artfynd.xlsx
+++ b/artfynd/A 26488-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115383182</v>
+        <v>115383349</v>
       </c>
       <c r="B2" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +709,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hammarkärret, Vrm</t>
+          <t>Hammaren, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>405421</v>
+        <v>405369</v>
       </c>
       <c r="R2" t="n">
-        <v>6698133</v>
+        <v>6698193</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,56 +776,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115383133</v>
+        <v>130157689</v>
       </c>
       <c r="B3" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hammarkärret, Vrm</t>
+          <t>Stöllet, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>405379</v>
+        <v>405387</v>
       </c>
       <c r="R3" t="n">
-        <v>6698085</v>
+        <v>6698139</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -854,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,56 +855,50 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Jonas Göransson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115383349</v>
+        <v>115383182</v>
       </c>
       <c r="B4" t="n">
-        <v>89736</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -926,14 +907,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hammaren, Vrm</t>
+          <t>Hammarkärret, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>405369</v>
+        <v>405421</v>
       </c>
       <c r="R4" t="n">
-        <v>6698193</v>
+        <v>6698133</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,37 +974,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115383393</v>
+        <v>115383388</v>
       </c>
       <c r="B5" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1102,16 +1078,11 @@
         <v>115383438</v>
       </c>
       <c r="B6" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1205,15 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115383321</v>
+        <v>115383133</v>
       </c>
       <c r="B7" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,38 +1187,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>6434</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hammaren, Vrm</t>
+          <t>Hammarkärret, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405359</v>
+        <v>405379</v>
       </c>
       <c r="R7" t="n">
-        <v>6698178</v>
+        <v>6698085</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,6 +1258,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1311,54 +1277,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115383425</v>
+        <v>115383189</v>
       </c>
       <c r="B8" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6434</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hammaren, Vrm</t>
+          <t>Hammarkärret, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405423</v>
+        <v>405421</v>
       </c>
       <c r="R8" t="n">
-        <v>6698106</v>
+        <v>6698133</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,6 +1359,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1417,37 +1378,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115383388</v>
+        <v>115383393</v>
       </c>
       <c r="B9" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1523,19 +1479,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115383257</v>
+        <v>115383007</v>
       </c>
       <c r="B10" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1566,10 +1517,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>405428</v>
+        <v>405438</v>
       </c>
       <c r="R10" t="n">
-        <v>6698127</v>
+        <v>6698076</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,37 +1580,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115383189</v>
+        <v>115383257</v>
       </c>
       <c r="B11" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6434</v>
+        <v>6450</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1672,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>405421</v>
+        <v>405428</v>
       </c>
       <c r="R11" t="n">
-        <v>6698133</v>
+        <v>6698127</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,48 +1681,52 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130157689</v>
+        <v>115383321</v>
       </c>
       <c r="B12" t="n">
-        <v>93079</v>
+        <v>58327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stöllet, Vrm</t>
+          <t>Hammaren, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405387</v>
+        <v>405359</v>
       </c>
       <c r="R12" t="n">
-        <v>6698139</v>
+        <v>6698178</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1800,12 +1750,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1820,15 +1770,116 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>August Oljeqvist, Jonas Göransson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>115383425</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hammaren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>405423</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6698106</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-03-24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-03-24</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>August Oljeqvist, Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26488-2025 artfynd.xlsx
+++ b/artfynd/A 26488-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115383349</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130157689</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115383182</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115383388</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115383438</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115383133</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115383189</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115383393</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1577,6 +1622,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115383007</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1678,6 +1728,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115383257</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1779,6 +1834,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115383321</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1880,8 +1940,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115383425</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>